--- a/data/bhagavadgita_ai_refined.xlsx
+++ b/data/bhagavadgita_ai_refined.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enric\Desktop\bhagavadgita\_GITHUB\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C922D4B-5802-4031-8B79-49FF69622CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FA92C4-AD5B-4ADB-9FDF-8513BA934842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12429,24 +12429,12 @@
     <t>For one who whose self has been conquered by the self, the self is a friend; but for one who has not mastered the self, the self remains hostile, like an enemy.</t>
   </si>
   <si>
-    <t xml:space="preserve">Let one lift one's own self by the self; let one not drag the self down. For the self alone is the friend of self, and the self alone is the enemy of the self. </t>
-  </si>
-  <si>
     <t>Let the yogin discipline the atman constantly, staying in solitude, alone, his mind and the self controlled, free of longing and of possessions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Si elevi il proprio sé attraverso il sé; non si lasci il sé sprofondare. Perché il sé è amico del sé, ed esso stesso è il proprio nemico. </t>
-  </si>
-  <si>
     <t>Per chi ha dominato il proprio sé attraverso il sé, esso è un amico; ma per chi non ha padroneggiato il sé, esso rimane ostile come un nemico.</t>
   </si>
   <si>
-    <t>Per chi ha dominato il sé ed è in pace, l'Atman [il Sé] supremo resta saldo, imperturbabile nel freddo e nel caldo, nel piacere e nel dolore, nell'onore e nel disonore.</t>
-  </si>
-  <si>
-    <t>For one who has mastered the self and is at peace, the supreme Atman [Self] stays steady, alike in cold and heat, pleasure and pain, honor and dishonor.</t>
-  </si>
-  <si>
     <t>Lo yogin appagato dalla conoscenza e dalla realizzazione, incrollabile, con i sensi soggiogati, per il quale una zolla di terra, una pietra e dell’oro sono la stessa cosa, è detto saldo nello yoga.</t>
   </si>
   <si>
@@ -12469,6 +12457,18 @@
   </si>
   <si>
     <t>Tu solo, o Krishna, puoi dissipare interamente questo mio dubbio; nessun altro, infatti, sarebbe in grado di toglierlo.</t>
+  </si>
+  <si>
+    <t>For one who has mastered the self and is at peace, the supreme Atman stays steady, alike in cold and heat, pleasure and pain, honor and dishonor.</t>
+  </si>
+  <si>
+    <t>Per chi ha dominato il sé ed è in pace, l'Atman supremo resta saldo, imperturbabile nel freddo e nel caldo, nel piacere e nel dolore, nell'onore e nel disonore.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let one lift one's own self by the self; let one not drag the self down. For the self alone is the friend of self, but the self alone is also the enemy of the self. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si elevi il proprio sé attraverso il sé; non si lasci il sé sprofondare. Perché il sé è amico del sé, ma esso è anche il proprio stesso nemico. </t>
   </si>
 </sst>
 </file>
@@ -22657,10 +22657,10 @@
         <v>1017</v>
       </c>
       <c r="M239" s="1" t="s">
-        <v>3595</v>
+        <v>3607</v>
       </c>
       <c r="N239" t="s">
-        <v>3597</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.35">
@@ -22701,7 +22701,7 @@
         <v>3594</v>
       </c>
       <c r="N240" t="s">
-        <v>3598</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.35">
@@ -22739,10 +22739,10 @@
         <v>1023</v>
       </c>
       <c r="M241" s="1" t="s">
-        <v>3600</v>
+        <v>3605</v>
       </c>
       <c r="N241" t="s">
-        <v>3599</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.35">
@@ -22783,7 +22783,7 @@
         <v>1027</v>
       </c>
       <c r="N242" t="s">
-        <v>3601</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.35">
@@ -22862,7 +22862,7 @@
         <v>1035</v>
       </c>
       <c r="M244" s="1" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="N244" t="s">
         <v>3591</v>
@@ -23152,7 +23152,7 @@
         <v>1063</v>
       </c>
       <c r="N251" t="s">
-        <v>3602</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.35">
@@ -23313,10 +23313,10 @@
         <v>1079</v>
       </c>
       <c r="M255" s="1" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="N255" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.35">
@@ -23764,10 +23764,10 @@
         <v>1123</v>
       </c>
       <c r="M266" s="1" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="N266" t="s">
-        <v>3606</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.35">
@@ -23805,7 +23805,7 @@
         <v>1126</v>
       </c>
       <c r="M267" s="1" t="s">
-        <v>3607</v>
+        <v>3603</v>
       </c>
       <c r="N267" t="s">
         <v>3057</v>
@@ -24054,7 +24054,7 @@
         <v>1150</v>
       </c>
       <c r="N273" t="s">
-        <v>3608</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.35">
